--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6464-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6464-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D89F2C4B-E6B0-466E-B485-37C788A21453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E53C004-5AE9-4B2F-9404-332DA9ABD11E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{DEAB067F-4921-4CB7-8165-988650E0AFFF}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{6FE968AD-C073-49D6-82EA-5529E01470EE}"/>
   </bookViews>
   <sheets>
     <sheet name="6464-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1526,23 +1526,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{180F4821-7358-4E67-BDCD-9DC8B0049E37}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B849FEB-6363-43ED-915F-48B843B2D202}">
   <dimension ref="A1:R33"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.77734375" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="7" width="7.6640625" customWidth="1"/>
-    <col min="8" max="8" width="7.44140625" customWidth="1"/>
-    <col min="9" max="10" width="7.6640625" customWidth="1"/>
-    <col min="11" max="13" width="7.44140625" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" customWidth="1"/>
-    <col min="15" max="17" width="7.44140625" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="14.25" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="7" width="9.75" customWidth="1"/>
+    <col min="8" max="8" width="9.25" customWidth="1"/>
+    <col min="9" max="10" width="9.75" customWidth="1"/>
+    <col min="11" max="13" width="9.25" customWidth="1"/>
+    <col min="14" max="14" width="9.75" customWidth="1"/>
+    <col min="15" max="17" width="9.25" customWidth="1"/>
+    <col min="18" max="18" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
@@ -1570,7 +1570,7 @@
       <c r="Q1" s="33"/>
       <c r="R1" s="25"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
@@ -1600,7 +1600,7 @@
       <c r="Q2" s="35"/>
       <c r="R2" s="36"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
         <v>2</v>
       </c>
@@ -1646,7 +1646,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="28"/>
       <c r="B4" s="29"/>
       <c r="C4" s="7"/>
@@ -1696,7 +1696,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="40">
         <v>2026</v>
       </c>
@@ -1750,7 +1750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1806,7 +1806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="42">
         <v>2025</v>
       </c>
@@ -1860,7 +1860,7 @@
         <v>4.49</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="44" t="s">
         <v>26</v>
       </c>
@@ -1916,7 +1916,7 @@
         <v>4.49</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="45"/>
       <c r="B9" s="20" t="s">
         <v>29</v>
@@ -1938,7 +1938,7 @@
       <c r="Q9" s="49"/>
       <c r="R9" s="49"/>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>26</v>
       </c>
@@ -1994,7 +1994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="40">
         <v>2024</v>
       </c>
@@ -2048,7 +2048,7 @@
         <v>5.13</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>26</v>
       </c>
@@ -2104,7 +2104,7 @@
         <v>5.13</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>26</v>
       </c>
@@ -2160,7 +2160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="42">
         <v>2023</v>
       </c>
@@ -2214,7 +2214,7 @@
         <v>5.33</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>26</v>
       </c>
@@ -2270,7 +2270,7 @@
         <v>5.33</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>26</v>
       </c>
@@ -2326,7 +2326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="40">
         <v>2022</v>
       </c>
@@ -2380,7 +2380,7 @@
         <v>5.18</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>26</v>
       </c>
@@ -2436,7 +2436,7 @@
         <v>5.18</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>26</v>
       </c>
@@ -2492,7 +2492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="42">
         <v>2021</v>
       </c>
@@ -2546,7 +2546,7 @@
         <v>2.84</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>26</v>
       </c>
@@ -2602,7 +2602,7 @@
         <v>2.84</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>26</v>
       </c>
@@ -2658,7 +2658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="40">
         <v>2020</v>
       </c>
@@ -2712,7 +2712,7 @@
         <v>3.46</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>26</v>
       </c>
@@ -2768,7 +2768,7 @@
         <v>3.46</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="42">
         <v>2019</v>
       </c>
@@ -2822,7 +2822,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
         <v>26</v>
       </c>
@@ -2878,7 +2878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
         <v>26</v>
       </c>
@@ -2934,7 +2934,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="40">
         <v>2018</v>
       </c>
@@ -2988,7 +2988,7 @@
         <v>4.2699999999999996</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="42">
         <v>2017</v>
       </c>
@@ -3042,7 +3042,7 @@
         <v>1.89</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="40">
         <v>2016</v>
       </c>
@@ -3096,7 +3096,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="42">
         <v>2015</v>
       </c>
@@ -3150,7 +3150,7 @@
         <v>4.96</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="40">
         <v>2014</v>
       </c>
@@ -3204,7 +3204,7 @@
         <v>4.26</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="42" t="s">
         <v>47</v>
       </c>
